--- a/other/baggage_drop_off_time_confirmation_form.xlsx
+++ b/other/baggage_drop_off_time_confirmation_form.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -781,34 +781,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dropoff_status_choices</t>
+          <t>airport_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'on_time'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'On Time'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dropoff_status_choices</t>
+          <t>airport_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'late'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Late'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'early'}</t>
+          <t>on_time</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Early'}</t>
+          <t>On Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>dropoff_status_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Late</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dropoff_status_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>early</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Early</t>
         </is>
       </c>
     </row>
